--- a/data/nbgen.xlsx
+++ b/data/nbgen.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I217"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4.053158095817163</v>
+        <v>5.847471084774373</v>
       </c>
       <c r="I2" t="n">
         <v>11.13</v>
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.004255626470173</v>
+        <v>5.776919734760252</v>
       </c>
       <c r="I3" t="n">
         <v>11.13</v>
@@ -575,7 +575,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.513477521836314</v>
+        <v>5.068876597028092</v>
       </c>
       <c r="I4" t="n">
         <v>10.13</v>
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.824977474907887</v>
+        <v>5.518276034561596</v>
       </c>
       <c r="I5" t="n">
         <v>12.5</v>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.884262597271399</v>
+        <v>5.603806386593932</v>
       </c>
       <c r="I6" t="n">
         <v>12.5</v>
@@ -686,7 +686,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.873878483635044</v>
+        <v>5.588825277346736</v>
       </c>
       <c r="I7" t="n">
         <v>12.5</v>
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.542403652999995</v>
+        <v>5.110608183010038</v>
       </c>
       <c r="I8" t="n">
         <v>12.5</v>
@@ -760,7 +760,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.516542556337673</v>
+        <v>5.073298507103359</v>
       </c>
       <c r="I9" t="n">
         <v>12.5</v>
@@ -797,7 +797,7 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.533975095473457</v>
+        <v>5.098448344864658</v>
       </c>
       <c r="I10" t="n">
         <v>12.5</v>
@@ -834,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.335883999511801</v>
+        <v>4.812663303076516</v>
       </c>
       <c r="I11" t="n">
         <v>12.5</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.484669023138546</v>
+        <v>5.027314718821369</v>
       </c>
       <c r="I12" t="n">
         <v>12.5</v>
@@ -908,7 +908,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>3.583744242742839</v>
+        <v>5.170250046819469</v>
       </c>
       <c r="I13" t="n">
         <v>12.5</v>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.02955992951214</v>
+        <v>5.813426127272043</v>
       </c>
       <c r="I14" t="n">
         <v>11.13</v>
@@ -982,7 +982,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.192866212223842</v>
+        <v>6.049027291486233</v>
       </c>
       <c r="I15" t="n">
         <v>11.13</v>
@@ -1019,7 +1019,7 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>3.947619176051838</v>
+        <v>5.695210608608164</v>
       </c>
       <c r="I16" t="n">
         <v>11.13</v>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>3.859542470321704</v>
+        <v>5.56814278203346</v>
       </c>
       <c r="I17" t="n">
         <v>12.5</v>
@@ -1093,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.995706230837737</v>
+        <v>5.764585564078736</v>
       </c>
       <c r="I18" t="n">
         <v>12.5</v>
@@ -1130,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.952833384053895</v>
+        <v>5.702733120634894</v>
       </c>
       <c r="I19" t="n">
         <v>12.5</v>
@@ -1167,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.743707708528141</v>
+        <v>5.401028545631329</v>
       </c>
       <c r="I20" t="n">
         <v>12.5</v>
@@ -1204,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>3.854664509089546</v>
+        <v>5.561105371554184</v>
       </c>
       <c r="I21" t="n">
         <v>12.5</v>
@@ -1241,7 +1241,7 @@
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.795087996215623</v>
+        <v>5.475154631877515</v>
       </c>
       <c r="I22" t="n">
         <v>12.5</v>
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.580376787284831</v>
+        <v>5.165391835529785</v>
       </c>
       <c r="I23" t="n">
         <v>12.5</v>
@@ -1315,7 +1315,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>3.811532190042765</v>
+        <v>5.498878588763348</v>
       </c>
       <c r="I24" t="n">
         <v>12.5</v>
@@ -1352,7 +1352,7 @@
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>3.738078077452093</v>
+        <v>5.392906704795886</v>
       </c>
       <c r="I25" t="n">
         <v>12.5</v>
@@ -1389,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>2.933380235939699</v>
+        <v>4.231973119431901</v>
       </c>
       <c r="I26" t="n">
         <v>12.63</v>
@@ -1426,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>2.884747023170538</v>
+        <v>4.161810224547338</v>
       </c>
       <c r="I27" t="n">
         <v>12.63</v>
@@ -1463,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.699317360344974</v>
+        <v>3.89429176955518</v>
       </c>
       <c r="I28" t="n">
         <v>12.63</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.595663093822759</v>
+        <v>2.302055232387637</v>
       </c>
       <c r="I29" t="n">
         <v>22.45</v>
@@ -1537,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.74081470965767</v>
+        <v>2.511464748729684</v>
       </c>
       <c r="I30" t="n">
         <v>22.45</v>
@@ -1574,7 +1574,7 @@
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>1.878957359815212</v>
+        <v>2.710762465047226</v>
       </c>
       <c r="I31" t="n">
         <v>22.45</v>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.797293287409381</v>
+        <v>2.592946112768536</v>
       </c>
       <c r="I32" t="n">
         <v>22.45</v>
@@ -1648,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.734168096790821</v>
+        <v>2.501875713307972</v>
       </c>
       <c r="I33" t="n">
         <v>22.45</v>
@@ -1685,7 +1685,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>1.808714828094525</v>
+        <v>2.609423912874303</v>
       </c>
       <c r="I34" t="n">
         <v>22.45</v>
@@ -1722,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.260904578452373</v>
+        <v>3.261795823256388</v>
       </c>
       <c r="I35" t="n">
         <v>22.11</v>
@@ -1759,7 +1759,7 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1.931994138743502</v>
+        <v>2.787278362991794</v>
       </c>
       <c r="I36" t="n">
         <v>20.95</v>
@@ -1796,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1.873366444910416</v>
+        <v>2.702696479840047</v>
       </c>
       <c r="I37" t="n">
         <v>20.95</v>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.010599634692316</v>
+        <v>4.343377163072731</v>
       </c>
       <c r="I38" t="n">
         <v>12.63</v>
@@ -1870,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>2.862219160467339</v>
+        <v>4.129309388743598</v>
       </c>
       <c r="I39" t="n">
         <v>12.63</v>
@@ -1907,7 +1907,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>2.77012846004618</v>
+        <v>3.996450591934003</v>
       </c>
       <c r="I40" t="n">
         <v>12.63</v>
@@ -1944,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>2.179671010398692</v>
+        <v>3.144600557471631</v>
       </c>
       <c r="I41" t="n">
         <v>20.95</v>
@@ -1981,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2.246922216679234</v>
+        <v>3.241623539266367</v>
       </c>
       <c r="I42" t="n">
         <v>20.95</v>
@@ -2018,7 +2018,7 @@
         <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>2.400362607469534</v>
+        <v>3.462991230131595</v>
       </c>
       <c r="I43" t="n">
         <v>20.95</v>
@@ -2055,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.433243616779044</v>
+        <v>3.510428499201851</v>
       </c>
       <c r="I44" t="n">
         <v>20.95</v>
@@ -2092,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2.225583311685427</v>
+        <v>3.210838006853801</v>
       </c>
       <c r="I45" t="n">
         <v>20.95</v>
@@ -2129,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>2.297312262740303</v>
+        <v>3.314321008828837</v>
       </c>
       <c r="I46" t="n">
         <v>20.95</v>
@@ -2166,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.475422158981186</v>
+        <v>3.571279272868811</v>
       </c>
       <c r="I47" t="n">
         <v>20.95</v>
@@ -2203,7 +2203,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>2.320849650858134</v>
+        <v>3.348278281941909</v>
       </c>
       <c r="I48" t="n">
         <v>20.95</v>
@@ -2240,7 +2240,7 @@
         <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>2.461922709591701</v>
+        <v>3.551803684179868</v>
       </c>
       <c r="I49" t="n">
         <v>20.95</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>4.150390101335132</v>
+        <v>5.987747216950838</v>
       </c>
       <c r="I50" t="n">
         <v>11.13</v>
@@ -2314,7 +2314,7 @@
         <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>3.512385093358195</v>
+        <v>5.067300555880188</v>
       </c>
       <c r="I51" t="n">
         <v>10.13</v>
@@ -2351,7 +2351,7 @@
         <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>3.970746132012217</v>
+        <v>5.728575753283058</v>
       </c>
       <c r="I52" t="n">
         <v>11.13</v>
@@ -2685,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>4.263482977383978</v>
+        <v>6.150905748386377</v>
       </c>
       <c r="I62" t="n">
         <v>12.13</v>
@@ -2722,7 +2722,7 @@
         <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>4.299911765604991</v>
+        <v>6.203461380498426</v>
       </c>
       <c r="I63" t="n">
         <v>12.13</v>
@@ -2759,7 +2759,7 @@
         <v>3</v>
       </c>
       <c r="H64" t="n">
-        <v>4.181073354134918</v>
+        <v>6.032013793603431</v>
       </c>
       <c r="I64" t="n">
         <v>12.13</v>
@@ -3093,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>4.020544335393656</v>
+        <v>5.800419374346641</v>
       </c>
       <c r="I74" t="n">
         <v>11.13</v>
@@ -3130,7 +3130,7 @@
         <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>4.024105874307303</v>
+        <v>5.80555758887529</v>
       </c>
       <c r="I75" t="n">
         <v>11.13</v>
@@ -3167,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="H76" t="n">
-        <v>3.975419167676099</v>
+        <v>5.735317518661237</v>
       </c>
       <c r="I76" t="n">
         <v>11.13</v>
@@ -3501,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>4.3213053543955</v>
+        <v>6.234325804953314</v>
       </c>
       <c r="I86" t="n">
         <v>12.13</v>
@@ -3538,7 +3538,7 @@
         <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>4.275917533661129</v>
+        <v>6.168845021063076</v>
       </c>
       <c r="I87" t="n">
         <v>12.13</v>
@@ -3575,7 +3575,7 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>4.250252484387203</v>
+        <v>6.131818181751414</v>
       </c>
       <c r="I88" t="n">
         <v>12.13</v>
@@ -3909,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>4.438890882472432</v>
+        <v>6.403965863190214</v>
       </c>
       <c r="I98" t="n">
         <v>11.25</v>
@@ -3946,7 +3946,7 @@
         <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>4.533201352369737</v>
+        <v>6.540027110414961</v>
       </c>
       <c r="I99" t="n">
         <v>11.25</v>
@@ -3983,7 +3983,7 @@
         <v>3</v>
       </c>
       <c r="H100" t="n">
-        <v>4.507890736508935</v>
+        <v>6.50351161043074</v>
       </c>
       <c r="I100" t="n">
         <v>11.25</v>
@@ -4020,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>4.525478040092192</v>
+        <v>6.528884726092913</v>
       </c>
       <c r="I101" t="n">
         <v>11.25</v>
@@ -4057,7 +4057,7 @@
         <v>2</v>
       </c>
       <c r="H102" t="n">
-        <v>4.655804265432341</v>
+        <v>6.716905725088918</v>
       </c>
       <c r="I102" t="n">
         <v>11.25</v>
@@ -4094,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>4.512686805062712</v>
+        <v>6.510430874749035</v>
       </c>
       <c r="I103" t="n">
         <v>11.25</v>
@@ -4131,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>4.361890400923908</v>
+        <v>6.292877650314098</v>
       </c>
       <c r="I104" t="n">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>4.236891507398246</v>
+        <v>6.112542366508011</v>
       </c>
       <c r="I105" t="n">
         <v>13</v>
@@ -4205,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>4.213330532240956</v>
+        <v>6.078551064490085</v>
       </c>
       <c r="I106" t="n">
         <v>13</v>
@@ -4242,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>3.951888069994586</v>
+        <v>5.70136932072945</v>
       </c>
       <c r="I107" t="n">
         <v>13</v>
@@ -4279,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="H108" t="n">
-        <v>3.987750874488867</v>
+        <v>5.753108410925714</v>
       </c>
       <c r="I108" t="n">
         <v>13</v>
@@ -4316,7 +4316,7 @@
         <v>3</v>
       </c>
       <c r="H109" t="n">
-        <v>3.933733442878149</v>
+        <v>5.675177730219374</v>
       </c>
       <c r="I109" t="n">
         <v>13</v>
@@ -4353,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>3.843613736230319</v>
+        <v>5.545162476352184</v>
       </c>
       <c r="I110" t="n">
         <v>13</v>
@@ -4390,7 +4390,7 @@
         <v>2</v>
       </c>
       <c r="H111" t="n">
-        <v>3.836390965260403</v>
+        <v>5.534742220492406</v>
       </c>
       <c r="I111" t="n">
         <v>13</v>
@@ -4427,7 +4427,7 @@
         <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>3.802100869853556</v>
+        <v>5.485272069897341</v>
       </c>
       <c r="I112" t="n">
         <v>13</v>
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>4.493973976762856</v>
+        <v>6.483433970159828</v>
       </c>
       <c r="I113" t="n">
         <v>11.25</v>
@@ -4501,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="H114" t="n">
-        <v>4.537473772673577</v>
+        <v>6.546190909999906</v>
       </c>
       <c r="I114" t="n">
         <v>11.25</v>
@@ -4538,7 +4538,7 @@
         <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>4.690975399336031</v>
+        <v>6.767646945554219</v>
       </c>
       <c r="I115" t="n">
         <v>11.25</v>
@@ -4575,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>4.539004070439074</v>
+        <v>6.548398662997274</v>
       </c>
       <c r="I116" t="n">
         <v>11.25</v>
@@ -4612,7 +4612,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="n">
-        <v>4.616760008830235</v>
+        <v>6.660576769713867</v>
       </c>
       <c r="I117" t="n">
         <v>11.25</v>
@@ -4649,7 +4649,7 @@
         <v>3</v>
       </c>
       <c r="H118" t="n">
-        <v>4.73804576205228</v>
+        <v>6.835555124417791</v>
       </c>
       <c r="I118" t="n">
         <v>11.25</v>
@@ -4686,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>4.207961241351697</v>
+        <v>6.07080481515106</v>
       </c>
       <c r="I119" t="n">
         <v>13</v>
@@ -4723,7 +4723,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="n">
-        <v>4.066006380145739</v>
+        <v>5.866007240859144</v>
       </c>
       <c r="I120" t="n">
         <v>13</v>
@@ -4760,7 +4760,7 @@
         <v>3</v>
       </c>
       <c r="H121" t="n">
-        <v>4.057282334738803</v>
+        <v>5.853421103814069</v>
       </c>
       <c r="I121" t="n">
         <v>13</v>
@@ -4797,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>3.943365803623267</v>
+        <v>5.689074289298411</v>
       </c>
       <c r="I122" t="n">
         <v>13</v>
@@ -4834,7 +4834,7 @@
         <v>2</v>
       </c>
       <c r="H123" t="n">
-        <v>3.779320462013064</v>
+        <v>5.45240688847643</v>
       </c>
       <c r="I123" t="n">
         <v>13</v>
@@ -4871,7 +4871,7 @@
         <v>3</v>
       </c>
       <c r="H124" t="n">
-        <v>3.847187755621782</v>
+        <v>5.550318696404286</v>
       </c>
       <c r="I124" t="n">
         <v>13</v>
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>3.903414876141747</v>
+        <v>5.631437284341906</v>
       </c>
       <c r="I125" t="n">
         <v>13</v>
@@ -4945,7 +4945,7 @@
         <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>3.793789677600293</v>
+        <v>5.473281554049682</v>
       </c>
       <c r="I126" t="n">
         <v>13</v>
@@ -4982,7 +4982,7 @@
         <v>3</v>
       </c>
       <c r="H127" t="n">
-        <v>3.964608985122002</v>
+        <v>5.71972172189934</v>
       </c>
       <c r="I127" t="n">
         <v>13</v>
@@ -5019,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>4.548886136070704</v>
+        <v>6.562655470077767</v>
       </c>
       <c r="I128" t="n">
         <v>11.25</v>
@@ -5056,7 +5056,7 @@
         <v>2</v>
       </c>
       <c r="H129" t="n">
-        <v>4.540350472485459</v>
+        <v>6.550341110552631</v>
       </c>
       <c r="I129" t="n">
         <v>11.25</v>
@@ -5093,7 +5093,7 @@
         <v>3</v>
       </c>
       <c r="H130" t="n">
-        <v>4.431535281189015</v>
+        <v>6.39335397369587</v>
       </c>
       <c r="I130" t="n">
         <v>11.25</v>
@@ -5130,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>4.516201877180324</v>
+        <v>6.515502051861482</v>
       </c>
       <c r="I131" t="n">
         <v>11.25</v>
@@ -5167,7 +5167,7 @@
         <v>2</v>
       </c>
       <c r="H132" t="n">
-        <v>4.539862119259992</v>
+        <v>6.54963656577605</v>
       </c>
       <c r="I132" t="n">
         <v>11.25</v>
@@ -5204,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="H133" t="n">
-        <v>4.532101519699335</v>
+        <v>6.538440387275563</v>
       </c>
       <c r="I133" t="n">
         <v>11.25</v>
@@ -5241,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>4.455951362188221</v>
+        <v>6.428578932671369</v>
       </c>
       <c r="I134" t="n">
         <v>18.25</v>
@@ -5278,7 +5278,7 @@
         <v>2</v>
       </c>
       <c r="H135" t="n">
-        <v>4.367371737600553</v>
+        <v>6.300785547554932</v>
       </c>
       <c r="I135" t="n">
         <v>18.25</v>
@@ -5315,7 +5315,7 @@
         <v>3</v>
       </c>
       <c r="H136" t="n">
-        <v>4.316610244636873</v>
+        <v>6.22755219338811</v>
       </c>
       <c r="I136" t="n">
         <v>18.25</v>
@@ -5352,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>4.277084589139262</v>
+        <v>6.170528726213826</v>
       </c>
       <c r="I137" t="n">
         <v>18.25</v>
@@ -5389,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>4.269037861037841</v>
+        <v>6.158919751486522</v>
       </c>
       <c r="I138" t="n">
         <v>18.25</v>
@@ -5426,7 +5426,7 @@
         <v>3</v>
       </c>
       <c r="H139" t="n">
-        <v>4.167269553568442</v>
+        <v>6.012099118980755</v>
       </c>
       <c r="I139" t="n">
         <v>18.25</v>
@@ -5463,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>4.294840328119686</v>
+        <v>6.1961448427882</v>
       </c>
       <c r="I140" t="n">
         <v>18.25</v>
@@ -5500,7 +5500,7 @@
         <v>2</v>
       </c>
       <c r="H141" t="n">
-        <v>4.367305110416638</v>
+        <v>6.300689424847111</v>
       </c>
       <c r="I141" t="n">
         <v>18.25</v>
@@ -5537,7 +5537,7 @@
         <v>3</v>
       </c>
       <c r="H142" t="n">
-        <v>4.269752290990098</v>
+        <v>6.159950456035707</v>
       </c>
       <c r="I142" t="n">
         <v>18.25</v>
@@ -5574,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>4.536078260467086</v>
+        <v>6.544177611460103</v>
       </c>
       <c r="I143" t="n">
         <v>11.25</v>
@@ -5611,7 +5611,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>4.537587637795477</v>
+        <v>6.546355182646602</v>
       </c>
       <c r="I144" t="n">
         <v>11.25</v>
@@ -5648,7 +5648,7 @@
         <v>3</v>
       </c>
       <c r="H145" t="n">
-        <v>4.546788146613089</v>
+        <v>6.559628711091425</v>
       </c>
       <c r="I145" t="n">
         <v>11.25</v>
@@ -5685,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>4.459202005718229</v>
+        <v>6.433268619971809</v>
       </c>
       <c r="I146" t="n">
         <v>11.25</v>
@@ -5722,7 +5722,7 @@
         <v>2</v>
       </c>
       <c r="H147" t="n">
-        <v>4.665355437507168</v>
+        <v>6.730685153675957</v>
       </c>
       <c r="I147" t="n">
         <v>11.25</v>
@@ -5759,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="H148" t="n">
-        <v>4.584414183112036</v>
+        <v>6.613911607356763</v>
       </c>
       <c r="I148" t="n">
         <v>11.25</v>
@@ -5796,7 +5796,7 @@
         <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>4.403076370568225</v>
+        <v>6.352296444474153</v>
       </c>
       <c r="I149" t="n">
         <v>17.5</v>
@@ -5833,7 +5833,7 @@
         <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>4.405251168724932</v>
+        <v>6.355434014989767</v>
       </c>
       <c r="I150" t="n">
         <v>17.5</v>
@@ -5870,7 +5870,7 @@
         <v>3</v>
       </c>
       <c r="H151" t="n">
-        <v>4.495640118639732</v>
+        <v>6.485837704783011</v>
       </c>
       <c r="I151" t="n">
         <v>17.5</v>
@@ -5907,7 +5907,7 @@
         <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>4.291976098132586</v>
+        <v>6.192012632389844</v>
       </c>
       <c r="I152" t="n">
         <v>17.5</v>
@@ -5944,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>4.337375097739602</v>
+        <v>6.257509543984206</v>
       </c>
       <c r="I153" t="n">
         <v>17.5</v>
@@ -5981,7 +5981,7 @@
         <v>3</v>
       </c>
       <c r="H154" t="n">
-        <v>4.21005576513414</v>
+        <v>6.073826574225009</v>
       </c>
       <c r="I154" t="n">
         <v>17.5</v>
@@ -6018,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>4.320560116632543</v>
+        <v>6.233250654128415</v>
       </c>
       <c r="I155" t="n">
         <v>17.5</v>
@@ -6055,7 +6055,7 @@
         <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>4.332974811190538</v>
+        <v>6.251161272401381</v>
       </c>
       <c r="I156" t="n">
         <v>17.5</v>
@@ -6092,7 +6092,7 @@
         <v>3</v>
       </c>
       <c r="H157" t="n">
-        <v>4.439288396230123</v>
+        <v>6.404539354317116</v>
       </c>
       <c r="I157" t="n">
         <v>17.5</v>
@@ -6129,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>4.515455146910286</v>
+        <v>6.514424747804014</v>
       </c>
       <c r="I158" t="n">
         <v>11.25</v>
@@ -6166,7 +6166,7 @@
         <v>2</v>
       </c>
       <c r="H159" t="n">
-        <v>4.527542443352891</v>
+        <v>6.531863030439521</v>
       </c>
       <c r="I159" t="n">
         <v>11.25</v>
@@ -6203,7 +6203,7 @@
         <v>3</v>
       </c>
       <c r="H160" t="n">
-        <v>4.784113127383227</v>
+        <v>6.902016283927569</v>
       </c>
       <c r="I160" t="n">
         <v>11.25</v>
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>3.882990034669735</v>
+        <v>5.601970466839294</v>
       </c>
       <c r="I161" t="n">
         <v>12</v>
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>4.061827248462655</v>
+        <v>5.859978028304736</v>
       </c>
       <c r="I162" t="n">
         <v>12</v>
@@ -6314,7 +6314,7 @@
         <v>3</v>
       </c>
       <c r="H163" t="n">
-        <v>4.165308629385221</v>
+        <v>6.009270103386063</v>
       </c>
       <c r="I163" t="n">
         <v>12</v>
@@ -6351,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>4.025603792427317</v>
+        <v>5.807718627918694</v>
       </c>
       <c r="I164" t="n">
         <v>18.25</v>
@@ -6388,7 +6388,7 @@
         <v>2</v>
       </c>
       <c r="H165" t="n">
-        <v>3.97253659662344</v>
+        <v>5.731158847698557</v>
       </c>
       <c r="I165" t="n">
         <v>18.25</v>
@@ -6425,7 +6425,7 @@
         <v>3</v>
       </c>
       <c r="H166" t="n">
-        <v>4.071816191189005</v>
+        <v>5.874389026439763</v>
       </c>
       <c r="I166" t="n">
         <v>18.25</v>
@@ -6462,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>4.002231880756256</v>
+        <v>5.774000086854761</v>
       </c>
       <c r="I167" t="n">
         <v>18.25</v>
@@ -6499,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="H168" t="n">
-        <v>4.179277473795274</v>
+        <v>6.029422885943399</v>
       </c>
       <c r="I168" t="n">
         <v>18.25</v>
@@ -6536,7 +6536,7 @@
         <v>3</v>
       </c>
       <c r="H169" t="n">
-        <v>4.148194323406579</v>
+        <v>5.984579379022421</v>
       </c>
       <c r="I169" t="n">
         <v>18.25</v>
@@ -6573,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>3.574433122011196</v>
+        <v>5.156816939114806</v>
       </c>
       <c r="I170" t="n">
         <v>17.08</v>
@@ -6610,7 +6610,7 @@
         <v>2</v>
       </c>
       <c r="H171" t="n">
-        <v>3.649614239158324</v>
+        <v>5.265280363991462</v>
       </c>
       <c r="I171" t="n">
         <v>17.08</v>
@@ -6647,7 +6647,7 @@
         <v>3</v>
       </c>
       <c r="H172" t="n">
-        <v>3.769161869405868</v>
+        <v>5.437751137299621</v>
       </c>
       <c r="I172" t="n">
         <v>17.08</v>
@@ -6684,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>4.544110591096803</v>
+        <v>6.555765815026375</v>
       </c>
       <c r="I173" t="n">
         <v>11.25</v>
@@ -6721,7 +6721,7 @@
         <v>2</v>
       </c>
       <c r="H174" t="n">
-        <v>4.613403023881757</v>
+        <v>6.655733664176358</v>
       </c>
       <c r="I174" t="n">
         <v>11.25</v>
@@ -6758,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="H175" t="n">
-        <v>4.453755573130524</v>
+        <v>6.425411078686994</v>
       </c>
       <c r="I175" t="n">
         <v>11.25</v>
@@ -6795,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>4.000947520210991</v>
+        <v>5.772147146265391</v>
       </c>
       <c r="I176" t="n">
         <v>12</v>
@@ -6832,7 +6832,7 @@
         <v>2</v>
       </c>
       <c r="H177" t="n">
-        <v>4.184393107195678</v>
+        <v>6.036803184881168</v>
       </c>
       <c r="I177" t="n">
         <v>12</v>
@@ -6869,7 +6869,7 @@
         <v>3</v>
       </c>
       <c r="H178" t="n">
-        <v>4.166484122022867</v>
+        <v>6.010965980784999</v>
       </c>
       <c r="I178" t="n">
         <v>12</v>
@@ -6906,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>4.300168281813685</v>
+        <v>6.203831455160619</v>
       </c>
       <c r="I179" t="n">
         <v>17.5</v>
@@ -6943,7 +6943,7 @@
         <v>2</v>
       </c>
       <c r="H180" t="n">
-        <v>4.332076559607378</v>
+        <v>6.249865369296888</v>
       </c>
       <c r="I180" t="n">
         <v>17.5</v>
@@ -6980,7 +6980,7 @@
         <v>3</v>
       </c>
       <c r="H181" t="n">
-        <v>4.229443527371746</v>
+        <v>6.101797202659146</v>
       </c>
       <c r="I181" t="n">
         <v>17.5</v>
@@ -7017,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>4.171454844410009</v>
+        <v>6.018137217322565</v>
       </c>
       <c r="I182" t="n">
         <v>17.5</v>
@@ -7054,7 +7054,7 @@
         <v>2</v>
       </c>
       <c r="H183" t="n">
-        <v>4.25884529942834</v>
+        <v>6.144214993398538</v>
       </c>
       <c r="I183" t="n">
         <v>17.5</v>
@@ -7091,7 +7091,7 @@
         <v>3</v>
       </c>
       <c r="H184" t="n">
-        <v>4.276703553246498</v>
+        <v>6.169979007620931</v>
       </c>
       <c r="I184" t="n">
         <v>17.5</v>
@@ -7128,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>4.192918593551255</v>
+        <v>6.049102861767519</v>
       </c>
       <c r="I185" t="n">
         <v>17.5</v>
@@ -7165,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="H186" t="n">
-        <v>4.297371278032659</v>
+        <v>6.199796231676384</v>
       </c>
       <c r="I186" t="n">
         <v>17.5</v>
@@ -7202,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="H187" t="n">
-        <v>4.133003506709302</v>
+        <v>5.962663663106203</v>
       </c>
       <c r="I187" t="n">
         <v>17.5</v>
@@ -7239,7 +7239,7 @@
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>4.564386258440361</v>
+        <v>6.585017419753638</v>
       </c>
       <c r="I188" t="n">
         <v>11.25</v>
@@ -7276,7 +7276,7 @@
         <v>2</v>
       </c>
       <c r="H189" t="n">
-        <v>4.536024852355075</v>
+        <v>6.544100559841754</v>
       </c>
       <c r="I189" t="n">
         <v>11.25</v>
@@ -7313,7 +7313,7 @@
         <v>3</v>
       </c>
       <c r="H190" t="n">
-        <v>4.683999448542462</v>
+        <v>6.757582775938849</v>
       </c>
       <c r="I190" t="n">
         <v>11.25</v>
@@ -7350,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="H191" t="n">
-        <v>3.972791786789202</v>
+        <v>5.731527009285183</v>
       </c>
       <c r="I191" t="n">
         <v>11.25</v>
@@ -7387,7 +7387,7 @@
         <v>2</v>
       </c>
       <c r="H192" t="n">
-        <v>3.964903103311578</v>
+        <v>5.720146044752876</v>
       </c>
       <c r="I192" t="n">
         <v>11.25</v>
@@ -7424,7 +7424,7 @@
         <v>3</v>
       </c>
       <c r="H193" t="n">
-        <v>4.095482729769815</v>
+        <v>5.908532624285305</v>
       </c>
       <c r="I193" t="n">
         <v>11.25</v>
@@ -7461,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>3.209128864988985</v>
+        <v>4.629794299093239</v>
       </c>
       <c r="I194" t="n">
         <v>17.75</v>
@@ -7498,7 +7498,7 @@
         <v>2</v>
       </c>
       <c r="H195" t="n">
-        <v>3.217683860568475</v>
+        <v>4.642136548790592</v>
       </c>
       <c r="I195" t="n">
         <v>17.75</v>
@@ -7535,7 +7535,7 @@
         <v>3</v>
       </c>
       <c r="H196" t="n">
-        <v>3.167516499859135</v>
+        <v>4.569760346280741</v>
       </c>
       <c r="I196" t="n">
         <v>17.75</v>
@@ -7572,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>2.818600568395791</v>
+        <v>4.066381062271419</v>
       </c>
       <c r="I197" t="n">
         <v>17.75</v>
@@ -7609,7 +7609,7 @@
         <v>2</v>
       </c>
       <c r="H198" t="n">
-        <v>2.91626589172551</v>
+        <v>4.207282339906024</v>
       </c>
       <c r="I198" t="n">
         <v>17.75</v>
@@ -7646,7 +7646,7 @@
         <v>3</v>
       </c>
       <c r="H199" t="n">
-        <v>2.788511281857083</v>
+        <v>4.02297139779814</v>
       </c>
       <c r="I199" t="n">
         <v>17.75</v>
@@ -7683,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>2.232595235784854</v>
+        <v>3.220954074979134</v>
       </c>
       <c r="I200" t="n">
         <v>20.42</v>
@@ -7720,7 +7720,7 @@
         <v>2</v>
       </c>
       <c r="H201" t="n">
-        <v>2.366895715396254</v>
+        <v>3.41470871090351</v>
       </c>
       <c r="I201" t="n">
         <v>20.42</v>
@@ -7757,7 +7757,7 @@
         <v>3</v>
       </c>
       <c r="H202" t="n">
-        <v>2.365187282537927</v>
+        <v>3.412243963291111</v>
       </c>
       <c r="I202" t="n">
         <v>20.42</v>
@@ -7794,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="H203" t="n">
-        <v>4.374556836734378</v>
+        <v>6.311151454443594</v>
       </c>
       <c r="I203" t="n">
         <v>11.25</v>
@@ -7831,7 +7831,7 @@
         <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>4.472131289514522</v>
+        <v>6.451921633586968</v>
       </c>
       <c r="I204" t="n">
         <v>11.25</v>
@@ -7868,7 +7868,7 @@
         <v>3</v>
       </c>
       <c r="H205" t="n">
-        <v>4.449969486685417</v>
+        <v>6.419948910548259</v>
       </c>
       <c r="I205" t="n">
         <v>11.25</v>
@@ -7905,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="H206" t="n">
-        <v>3.705530267124038</v>
+        <v>5.345950140243803</v>
       </c>
       <c r="I206" t="n">
         <v>12</v>
@@ -7942,7 +7942,7 @@
         <v>2</v>
       </c>
       <c r="H207" t="n">
-        <v>3.758047504886392</v>
+        <v>5.421716498724734</v>
       </c>
       <c r="I207" t="n">
         <v>12</v>
@@ -7979,7 +7979,7 @@
         <v>3</v>
       </c>
       <c r="H208" t="n">
-        <v>3.696719358025701</v>
+        <v>5.333238685381913</v>
       </c>
       <c r="I208" t="n">
         <v>12</v>
@@ -8016,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="H209" t="n">
-        <v>3.266977431133953</v>
+        <v>4.713252138593115</v>
       </c>
       <c r="I209" t="n">
         <v>17</v>
@@ -8053,7 +8053,7 @@
         <v>2</v>
       </c>
       <c r="H210" t="n">
-        <v>3.151012242622071</v>
+        <v>4.545949736211275</v>
       </c>
       <c r="I210" t="n">
         <v>17</v>
@@ -8090,7 +8090,7 @@
         <v>3</v>
       </c>
       <c r="H211" t="n">
-        <v>3.104326114133249</v>
+        <v>4.478595890162146</v>
       </c>
       <c r="I211" t="n">
         <v>17</v>
@@ -8127,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>3.269573389059604</v>
+        <v>4.71699731421881</v>
       </c>
       <c r="I212" t="n">
         <v>17</v>
@@ -8164,7 +8164,7 @@
         <v>2</v>
       </c>
       <c r="H213" t="n">
-        <v>3.288195813776118</v>
+        <v>4.743863794006652</v>
       </c>
       <c r="I213" t="n">
         <v>17</v>
@@ -8201,7 +8201,7 @@
         <v>3</v>
       </c>
       <c r="H214" t="n">
-        <v>3.168877811704205</v>
+        <v>4.571724304128729</v>
       </c>
       <c r="I214" t="n">
         <v>17</v>
@@ -8238,7 +8238,7 @@
         <v>1</v>
       </c>
       <c r="H215" t="n">
-        <v>2.90690780339289</v>
+        <v>4.193781472276351</v>
       </c>
       <c r="I215" t="n">
         <v>19.67</v>
@@ -8275,7 +8275,7 @@
         <v>2</v>
       </c>
       <c r="H216" t="n">
-        <v>2.5948912202635</v>
+        <v>3.743636695120458</v>
       </c>
       <c r="I216" t="n">
         <v>19.67</v>
@@ -8312,10 +8312,454 @@
         <v>3</v>
       </c>
       <c r="H217" t="n">
-        <v>2.384662349814906</v>
+        <v>3.440340546272589</v>
       </c>
       <c r="I217" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>101</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="n">
+        <v>4.845292230387768</v>
+      </c>
+      <c r="I218" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>102</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>2</v>
+      </c>
+      <c r="H219" t="n">
+        <v>4.996613231229626</v>
+      </c>
+      <c r="I219" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>103</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" t="n">
+        <v>4.848784178575054</v>
+      </c>
+      <c r="I220" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>104</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>caspofungin</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>6.101226312327134</v>
+      </c>
+      <c r="I221" t="n">
+        <v>22.15</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>105</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>caspofungin</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="n">
+        <v>6.412264110600665</v>
+      </c>
+      <c r="I222" t="n">
+        <v>22.15</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>106</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>caspofungin</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>3</v>
+      </c>
+      <c r="H223" t="n">
+        <v>6.38868986307611</v>
+      </c>
+      <c r="I223" t="n">
+        <v>22.15</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>107</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>micafungin</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
+        <v>5.817432843318178</v>
+      </c>
+      <c r="I224" t="n">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>108</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>micafungin</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>2</v>
+      </c>
+      <c r="H225" t="n">
+        <v>5.706665411668264</v>
+      </c>
+      <c r="I225" t="n">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>109</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>micafungin</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>3</v>
+      </c>
+      <c r="H226" t="n">
+        <v>5.713665262029995</v>
+      </c>
+      <c r="I226" t="n">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>110</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>anidulafungin</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>5.891035524787366</v>
+      </c>
+      <c r="I227" t="n">
+        <v>21.83</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>111</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>anidulafungin</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>2</v>
+      </c>
+      <c r="H228" t="n">
+        <v>6.510174980866346</v>
+      </c>
+      <c r="I228" t="n">
+        <v>21.83</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BY4741</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>112</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>FKS1-HS3</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>anidulafungin</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>3</v>
+      </c>
+      <c r="H229" t="n">
+        <v>6.1681203435318</v>
+      </c>
+      <c r="I229" t="n">
+        <v>21.83</v>
       </c>
     </row>
   </sheetData>
